--- a/test-data/Scenario-1.xlsx
+++ b/test-data/Scenario-1.xlsx
@@ -451,7 +451,7 @@
         <v>PO-SCENARIO-1</v>
       </c>
       <c r="C2" t="str">
-        <v>00188-002</v>
+        <v>110017-001</v>
       </c>
       <c r="D2" t="str">
         <v>Auto Ship</v>

--- a/test-data/Scenario-1.xlsx
+++ b/test-data/Scenario-1.xlsx
@@ -451,7 +451,7 @@
         <v>PO-SCENARIO-1</v>
       </c>
       <c r="C2" t="str">
-        <v>110017-001</v>
+        <v>100054-009</v>
       </c>
       <c r="D2" t="str">
         <v>Auto Ship</v>
